--- a/ETF Regime mode/walkforward/QQQ/wf_regime_QQQ_1e-07_1e-03_8_5.xlsx
+++ b/ETF Regime mode/walkforward/QQQ/wf_regime_QQQ_1e-07_1e-03_8_5.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="91" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93" uniqueCount="77">
   <si>
     <t>Ticker</t>
   </si>
@@ -51,6 +51,9 @@
     <t>BuyConfirmDays</t>
   </si>
   <si>
+    <t>RegimeRiskOffScale</t>
+  </si>
+  <si>
     <t>BuyHoldReturnPct</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
   </si>
   <si>
     <t>SPYRegimeRiskOnPct</t>
+  </si>
+  <si>
+    <t>AverageRegimeScalePct</t>
   </si>
   <si>
     <t>BuyHoldExcessReturnPct</t>
@@ -283,7 +289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="true"/>
@@ -296,69 +302,71 @@
     <col min="8" max="8" width="6.9453125" customWidth="true"/>
     <col min="9" max="9" width="13.9453125" customWidth="true"/>
     <col min="10" max="10" width="14.20703125" customWidth="true"/>
-    <col min="11" max="11" width="15.5234375" customWidth="true"/>
-    <col min="12" max="12" width="15.3671875" customWidth="true"/>
-    <col min="13" max="13" width="16.1015625" customWidth="true"/>
-    <col min="14" max="14" width="15.5234375" customWidth="true"/>
-    <col min="15" max="15" width="20.68359375" customWidth="true"/>
-    <col min="16" max="16" width="22.3125" customWidth="true"/>
-    <col min="17" max="17" width="22.15625" customWidth="true"/>
-    <col min="18" max="18" width="22.89453125" customWidth="true"/>
-    <col min="19" max="19" width="22.3125" customWidth="true"/>
-    <col min="20" max="20" width="27.47265625" customWidth="true"/>
-    <col min="21" max="21" width="13.20703125" customWidth="true"/>
-    <col min="22" max="22" width="14.15625" customWidth="true"/>
-    <col min="23" max="23" width="13.7890625" customWidth="true"/>
-    <col min="24" max="24" width="13.20703125" customWidth="true"/>
-    <col min="25" max="25" width="18.3671875" customWidth="true"/>
-    <col min="26" max="26" width="15.41796875" customWidth="true"/>
-    <col min="27" max="27" width="15.26171875" customWidth="true"/>
-    <col min="28" max="28" width="16" customWidth="true"/>
-    <col min="29" max="29" width="15.41796875" customWidth="true"/>
-    <col min="30" max="30" width="20.578125" customWidth="true"/>
-    <col min="31" max="31" width="15.15625" customWidth="true"/>
-    <col min="32" max="32" width="15" customWidth="true"/>
-    <col min="33" max="33" width="15.734375" customWidth="true"/>
-    <col min="34" max="34" width="15.15625" customWidth="true"/>
-    <col min="35" max="35" width="20.3125" customWidth="true"/>
-    <col min="36" max="36" width="16.99609375" customWidth="true"/>
-    <col min="37" max="37" width="16.83984375" customWidth="true"/>
-    <col min="38" max="38" width="17.578125" customWidth="true"/>
-    <col min="39" max="39" width="16.99609375" customWidth="true"/>
-    <col min="40" max="40" width="22.15625" customWidth="true"/>
-    <col min="41" max="41" width="21.3671875" customWidth="true"/>
-    <col min="42" max="42" width="21.20703125" customWidth="true"/>
-    <col min="43" max="43" width="21.9453125" customWidth="true"/>
-    <col min="44" max="44" width="21.3671875" customWidth="true"/>
-    <col min="45" max="45" width="26.5234375" customWidth="true"/>
-    <col min="46" max="46" width="17.20703125" customWidth="true"/>
-    <col min="47" max="47" width="23.83984375" customWidth="true"/>
-    <col min="48" max="48" width="29" customWidth="true"/>
-    <col min="49" max="49" width="19.5234375" customWidth="true"/>
-    <col min="50" max="50" width="24.1015625" customWidth="true"/>
-    <col min="51" max="51" width="27.20703125" customWidth="true"/>
-    <col min="52" max="52" width="25.41796875" customWidth="true"/>
-    <col min="53" max="53" width="14" customWidth="true"/>
-    <col min="54" max="54" width="21.734375" customWidth="true"/>
-    <col min="55" max="55" width="17.68359375" customWidth="true"/>
-    <col min="56" max="56" width="20.578125" customWidth="true"/>
-    <col min="57" max="57" width="20.41796875" customWidth="true"/>
-    <col min="58" max="58" width="21.15625" customWidth="true"/>
-    <col min="59" max="59" width="20.578125" customWidth="true"/>
-    <col min="60" max="60" width="25.734375" customWidth="true"/>
-    <col min="61" max="61" width="29.62890625" customWidth="true"/>
-    <col min="62" max="62" width="29.47265625" customWidth="true"/>
-    <col min="63" max="63" width="30.20703125" customWidth="true"/>
-    <col min="64" max="64" width="29.62890625" customWidth="true"/>
-    <col min="65" max="65" width="34.7890625" customWidth="true"/>
-    <col min="66" max="66" width="23.99609375" customWidth="true"/>
-    <col min="67" max="67" width="23.83984375" customWidth="true"/>
-    <col min="68" max="68" width="24.578125" customWidth="true"/>
-    <col min="69" max="69" width="23.99609375" customWidth="true"/>
-    <col min="70" max="70" width="29.15625" customWidth="true"/>
-    <col min="71" max="71" width="29.15625" customWidth="true"/>
-    <col min="72" max="72" width="43.26171875" customWidth="true"/>
-    <col min="73" max="73" width="37.62890625" customWidth="true"/>
+    <col min="11" max="11" width="16.578125" customWidth="true"/>
+    <col min="12" max="12" width="15.5234375" customWidth="true"/>
+    <col min="13" max="13" width="15.3671875" customWidth="true"/>
+    <col min="14" max="14" width="16.1015625" customWidth="true"/>
+    <col min="15" max="15" width="15.5234375" customWidth="true"/>
+    <col min="16" max="16" width="20.68359375" customWidth="true"/>
+    <col min="17" max="17" width="22.3125" customWidth="true"/>
+    <col min="18" max="18" width="22.15625" customWidth="true"/>
+    <col min="19" max="19" width="22.89453125" customWidth="true"/>
+    <col min="20" max="20" width="22.3125" customWidth="true"/>
+    <col min="21" max="21" width="27.47265625" customWidth="true"/>
+    <col min="22" max="22" width="13.20703125" customWidth="true"/>
+    <col min="23" max="23" width="14.15625" customWidth="true"/>
+    <col min="24" max="24" width="13.7890625" customWidth="true"/>
+    <col min="25" max="25" width="13.20703125" customWidth="true"/>
+    <col min="26" max="26" width="18.3671875" customWidth="true"/>
+    <col min="27" max="27" width="15.41796875" customWidth="true"/>
+    <col min="28" max="28" width="15.26171875" customWidth="true"/>
+    <col min="29" max="29" width="16" customWidth="true"/>
+    <col min="30" max="30" width="15.41796875" customWidth="true"/>
+    <col min="31" max="31" width="20.578125" customWidth="true"/>
+    <col min="32" max="32" width="15.15625" customWidth="true"/>
+    <col min="33" max="33" width="15" customWidth="true"/>
+    <col min="34" max="34" width="15.734375" customWidth="true"/>
+    <col min="35" max="35" width="15.15625" customWidth="true"/>
+    <col min="36" max="36" width="20.3125" customWidth="true"/>
+    <col min="37" max="37" width="16.99609375" customWidth="true"/>
+    <col min="38" max="38" width="16.83984375" customWidth="true"/>
+    <col min="39" max="39" width="17.578125" customWidth="true"/>
+    <col min="40" max="40" width="16.99609375" customWidth="true"/>
+    <col min="41" max="41" width="22.15625" customWidth="true"/>
+    <col min="42" max="42" width="21.3671875" customWidth="true"/>
+    <col min="43" max="43" width="21.20703125" customWidth="true"/>
+    <col min="44" max="44" width="21.9453125" customWidth="true"/>
+    <col min="45" max="45" width="21.3671875" customWidth="true"/>
+    <col min="46" max="46" width="26.5234375" customWidth="true"/>
+    <col min="47" max="47" width="17.20703125" customWidth="true"/>
+    <col min="48" max="48" width="23.83984375" customWidth="true"/>
+    <col min="49" max="49" width="29" customWidth="true"/>
+    <col min="50" max="50" width="19.5234375" customWidth="true"/>
+    <col min="51" max="51" width="24.1015625" customWidth="true"/>
+    <col min="52" max="52" width="27.20703125" customWidth="true"/>
+    <col min="53" max="53" width="25.41796875" customWidth="true"/>
+    <col min="54" max="54" width="14" customWidth="true"/>
+    <col min="55" max="55" width="21.734375" customWidth="true"/>
+    <col min="56" max="56" width="17.68359375" customWidth="true"/>
+    <col min="57" max="57" width="19.89453125" customWidth="true"/>
+    <col min="58" max="58" width="20.578125" customWidth="true"/>
+    <col min="59" max="59" width="20.41796875" customWidth="true"/>
+    <col min="60" max="60" width="21.15625" customWidth="true"/>
+    <col min="61" max="61" width="20.578125" customWidth="true"/>
+    <col min="62" max="62" width="25.734375" customWidth="true"/>
+    <col min="63" max="63" width="29.62890625" customWidth="true"/>
+    <col min="64" max="64" width="29.47265625" customWidth="true"/>
+    <col min="65" max="65" width="30.20703125" customWidth="true"/>
+    <col min="66" max="66" width="29.62890625" customWidth="true"/>
+    <col min="67" max="67" width="34.7890625" customWidth="true"/>
+    <col min="68" max="68" width="23.99609375" customWidth="true"/>
+    <col min="69" max="69" width="23.83984375" customWidth="true"/>
+    <col min="70" max="70" width="24.578125" customWidth="true"/>
+    <col min="71" max="71" width="23.99609375" customWidth="true"/>
+    <col min="72" max="72" width="29.15625" customWidth="true"/>
+    <col min="73" max="73" width="29.15625" customWidth="true"/>
+    <col min="74" max="74" width="43.26171875" customWidth="true"/>
+    <col min="75" max="75" width="37.62890625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +589,12 @@
       <c r="BU1" s="0" t="s">
         <v>74</v>
       </c>
+      <c r="BV1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="BW1" s="0" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -614,52 +628,52 @@
         <v>5</v>
       </c>
       <c r="K2" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="0">
         <v>-0.11405355793117078</v>
       </c>
-      <c r="L2" s="0">
+      <c r="M2" s="0">
         <v>-4.0975711656975555</v>
-      </c>
-      <c r="M2" s="0">
-        <v>-5.1274537952934356</v>
       </c>
       <c r="N2" s="0">
         <v>-5.1274537952934356</v>
       </c>
       <c r="O2" s="0">
-        <v>-7.3727849970136923</v>
+        <v>-5.1274537952934356</v>
       </c>
       <c r="P2" s="0">
+        <v>-5.4328059962784554</v>
+      </c>
+      <c r="Q2" s="0">
         <v>-22.799679280511707</v>
       </c>
-      <c r="Q2" s="0">
+      <c r="R2" s="0">
         <v>-22.799679280511796</v>
-      </c>
-      <c r="R2" s="0">
-        <v>-22.799679280511732</v>
       </c>
       <c r="S2" s="0">
         <v>-22.799679280511732</v>
       </c>
       <c r="T2" s="0">
-        <v>-22.799679280511743</v>
+        <v>-22.799679280511732</v>
       </c>
       <c r="U2" s="0">
+        <v>-22.799679280511732</v>
+      </c>
+      <c r="V2" s="0">
         <v>0.10929987296124369</v>
       </c>
-      <c r="V2" s="0">
+      <c r="W2" s="0">
         <v>-0.074846046557122278</v>
-      </c>
-      <c r="W2" s="0">
-        <v>-0.12407609018652926</v>
       </c>
       <c r="X2" s="0">
         <v>-0.12407609018652926</v>
       </c>
       <c r="Y2" s="0">
-        <v>-0.23308161798244795</v>
+        <v>-0.12407609018652926</v>
       </c>
       <c r="Z2" s="0">
-        <v>1</v>
+        <v>-0.13864502431942732</v>
       </c>
       <c r="AA2" s="0">
         <v>1</v>
@@ -674,10 +688,10 @@
         <v>1</v>
       </c>
       <c r="AE2" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="0">
         <v>1</v>
@@ -686,28 +700,28 @@
         <v>1</v>
       </c>
       <c r="AI2" s="0">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="0">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="0">
         <v>2</v>
-      </c>
-      <c r="AJ2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="0">
-        <v>2</v>
-      </c>
-      <c r="AL2" s="0">
-        <v>8</v>
       </c>
       <c r="AM2" s="0">
         <v>8</v>
       </c>
       <c r="AN2" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO2" s="0">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="AP2" s="0">
-        <v>96.414342629482078</v>
+        <v>100</v>
       </c>
       <c r="AQ2" s="0">
         <v>96.414342629482078</v>
@@ -716,91 +730,97 @@
         <v>96.414342629482078</v>
       </c>
       <c r="AS2" s="0">
-        <v>95.2191235059761</v>
+        <v>96.414342629482078</v>
       </c>
       <c r="AT2" s="0">
-        <v>95.916334661354583</v>
+        <v>96.414342629482078</v>
       </c>
       <c r="AU2" s="0">
         <v>95.916334661354583</v>
       </c>
       <c r="AV2" s="0">
-        <v>94.960159362549803</v>
+        <v>95.916334661354583</v>
       </c>
       <c r="AW2" s="0">
+        <v>95.4382470119522</v>
+      </c>
+      <c r="AX2" s="0">
         <v>2.4500000000000002</v>
       </c>
-      <c r="AX2" s="0">
-        <v>3.1999999999999997</v>
-      </c>
       <c r="AY2" s="0">
+        <v>2.8250000000000002</v>
+      </c>
+      <c r="AZ2" s="0">
         <v>9</v>
       </c>
-      <c r="AZ2" s="0">
+      <c r="BA2" s="0">
         <v>3</v>
       </c>
-      <c r="BA2" s="0">
-        <v>1</v>
-      </c>
       <c r="BB2" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC2" s="0">
         <v>0.046487603305785122</v>
       </c>
-      <c r="BC2" s="0">
+      <c r="BD2" s="0">
         <v>98.804780876494021</v>
       </c>
-      <c r="BD2" s="0">
-        <v>0</v>
-      </c>
       <c r="BE2" s="0">
+        <v>99.402390438247011</v>
+      </c>
+      <c r="BF2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="0">
         <v>-3.9835176077663847</v>
       </c>
-      <c r="BF2" s="0">
+      <c r="BH2" s="0">
         <v>-5.0134002373622639</v>
       </c>
-      <c r="BG2" s="0">
+      <c r="BI2" s="0">
         <v>-5.0134002373622639</v>
       </c>
-      <c r="BH2" s="0">
-        <v>-7.2587314390825224</v>
-      </c>
-      <c r="BI2" s="0">
-        <v>0</v>
-      </c>
       <c r="BJ2" s="0">
+        <v>-5.3187524383472855</v>
+      </c>
+      <c r="BK2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="0">
         <v>-8.8817841970012523e-14</v>
       </c>
-      <c r="BK2" s="0">
+      <c r="BM2" s="0">
         <v>-2.2204460492503131e-14</v>
       </c>
-      <c r="BL2" s="0">
+      <c r="BN2" s="0">
         <v>-2.2204460492503131e-14</v>
       </c>
-      <c r="BM2" s="0">
-        <v>-3.3306690738754696e-14</v>
-      </c>
-      <c r="BN2" s="0">
-        <v>0</v>
-      </c>
       <c r="BO2" s="0">
+        <v>-2.2204460492503131e-14</v>
+      </c>
+      <c r="BP2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="0">
         <v>-0.18414591951836595</v>
       </c>
-      <c r="BP2" s="0">
+      <c r="BR2" s="0">
         <v>-0.23337596314777295</v>
       </c>
-      <c r="BQ2" s="0">
+      <c r="BS2" s="0">
         <v>-0.23337596314777295</v>
       </c>
-      <c r="BR2" s="0">
-        <v>-0.34238149094369164</v>
-      </c>
-      <c r="BS2" s="0">
-        <v>-2.2453312017202576</v>
-      </c>
       <c r="BT2" s="0">
-        <v>-1.1102230246251565e-14</v>
+        <v>-0.24794489728067101</v>
       </c>
       <c r="BU2" s="0">
-        <v>-0.10900552779591868</v>
+        <v>-0.30535220098502069</v>
+      </c>
+      <c r="BV2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW2" s="0">
+        <v>-0.014568934132898059</v>
       </c>
     </row>
     <row r="3">
@@ -835,55 +855,55 @@
         <v>5</v>
       </c>
       <c r="K3" s="0">
-        <v>38.958968156911354</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="0">
         <v>38.958968156911354</v>
       </c>
       <c r="M3" s="0">
-        <v>39.956594321389161</v>
+        <v>38.958968156911354</v>
       </c>
       <c r="N3" s="0">
         <v>39.956594321389161</v>
       </c>
       <c r="O3" s="0">
-        <v>34.231854886127543</v>
+        <v>39.956594321389161</v>
       </c>
       <c r="P3" s="0">
-        <v>-10.977189830693035</v>
+        <v>37.10936527095938</v>
       </c>
       <c r="Q3" s="0">
         <v>-10.977189830693035</v>
       </c>
       <c r="R3" s="0">
-        <v>-10.977189830693012</v>
+        <v>-10.977189830693035</v>
       </c>
       <c r="S3" s="0">
         <v>-10.977189830693012</v>
       </c>
       <c r="T3" s="0">
-        <v>-10.977189830693002</v>
+        <v>-10.977189830693012</v>
       </c>
       <c r="U3" s="0">
-        <v>2.1156923103317657</v>
+        <v>-10.977189830692978</v>
       </c>
       <c r="V3" s="0">
         <v>2.1156923103317657</v>
       </c>
       <c r="W3" s="0">
-        <v>2.1785791236616663</v>
+        <v>2.1156923103317657</v>
       </c>
       <c r="X3" s="0">
         <v>2.1785791236616663</v>
       </c>
       <c r="Y3" s="0">
-        <v>2.013074174394379</v>
+        <v>2.1785791236616663</v>
       </c>
       <c r="Z3" s="0">
-        <v>1</v>
+        <v>2.1268149299964501</v>
       </c>
       <c r="AA3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="0">
         <v>0</v>
@@ -892,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="AD3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="0">
         <v>0</v>
@@ -916,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="0">
         <v>1</v>
@@ -925,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="AO3" s="0">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AP3" s="0">
         <v>100</v>
@@ -937,91 +957,97 @@
         <v>100</v>
       </c>
       <c r="AS3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="AT3" s="0">
-        <v>99.900793650793645</v>
+        <v>100</v>
       </c>
       <c r="AU3" s="0">
         <v>99.900793650793645</v>
       </c>
       <c r="AV3" s="0">
+        <v>99.900793650793645</v>
+      </c>
+      <c r="AW3" s="0">
+        <v>99.156746031746039</v>
+      </c>
+      <c r="AX3" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="AY3" s="0">
+        <v>0.625</v>
+      </c>
+      <c r="AZ3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="0">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="BC3" s="0">
+        <v>0.001984126984126984</v>
+      </c>
+      <c r="BD3" s="0">
         <v>98.412698412698404</v>
       </c>
-      <c r="AW3" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="AX3" s="0">
-        <v>1</v>
-      </c>
-      <c r="AY3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AZ3" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA3" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="BB3" s="0">
-        <v>0.001984126984126984</v>
-      </c>
-      <c r="BC3" s="0">
-        <v>98.412698412698404</v>
-      </c>
-      <c r="BD3" s="0">
-        <v>0</v>
-      </c>
       <c r="BE3" s="0">
-        <v>0</v>
+        <v>99.206349206349216</v>
       </c>
       <c r="BF3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH3" s="0">
         <v>0.99762616447780506</v>
       </c>
-      <c r="BG3" s="0">
+      <c r="BI3" s="0">
         <v>0.99762616447780506</v>
       </c>
-      <c r="BH3" s="0">
-        <v>-4.7271132707838115</v>
-      </c>
-      <c r="BI3" s="0">
-        <v>0</v>
-      </c>
       <c r="BJ3" s="0">
-        <v>0</v>
+        <v>-1.8496028859519731</v>
       </c>
       <c r="BK3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BM3" s="0">
         <v>2.2204460492503131e-14</v>
       </c>
-      <c r="BL3" s="0">
+      <c r="BN3" s="0">
         <v>2.2204460492503131e-14</v>
       </c>
-      <c r="BM3" s="0">
+      <c r="BO3" s="0">
+        <v>5.5511151231257827e-14</v>
+      </c>
+      <c r="BP3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BR3" s="0">
+        <v>0.062886813329900537</v>
+      </c>
+      <c r="BS3" s="0">
+        <v>0.062886813329900537</v>
+      </c>
+      <c r="BT3" s="0">
+        <v>0.011122619664684308</v>
+      </c>
+      <c r="BU3" s="0">
+        <v>-2.8472290504297781</v>
+      </c>
+      <c r="BV3" s="0">
         <v>3.3306690738754696e-14</v>
       </c>
-      <c r="BN3" s="0">
-        <v>0</v>
-      </c>
-      <c r="BO3" s="0">
-        <v>0</v>
-      </c>
-      <c r="BP3" s="0">
-        <v>0.062886813329900537</v>
-      </c>
-      <c r="BQ3" s="0">
-        <v>0.062886813329900537</v>
-      </c>
-      <c r="BR3" s="0">
-        <v>-0.10261813593738678</v>
-      </c>
-      <c r="BS3" s="0">
-        <v>-5.7247394352616165</v>
-      </c>
-      <c r="BT3" s="0">
-        <v>1.1102230246251565e-14</v>
-      </c>
-      <c r="BU3" s="0">
-        <v>-0.16550494926728732</v>
+      <c r="BW3" s="0">
+        <v>-0.051764193665216229</v>
       </c>
     </row>
     <row r="4">
@@ -1056,55 +1082,55 @@
         <v>5</v>
       </c>
       <c r="K4" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="0">
         <v>48.646611788845327</v>
       </c>
-      <c r="L4" s="0">
+      <c r="M4" s="0">
         <v>60.956505913153961</v>
-      </c>
-      <c r="M4" s="0">
-        <v>62.206214124895929</v>
       </c>
       <c r="N4" s="0">
         <v>62.206214124895929</v>
       </c>
       <c r="O4" s="0">
-        <v>61.565457091472872</v>
+        <v>62.206214124895929</v>
       </c>
       <c r="P4" s="0">
+        <v>63.241351058830197</v>
+      </c>
+      <c r="Q4" s="0">
         <v>-28.555538592397166</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="R4" s="0">
         <v>-15.080854712824621</v>
-      </c>
-      <c r="R4" s="0">
-        <v>-15.053337886935392</v>
       </c>
       <c r="S4" s="0">
         <v>-15.053337886935392</v>
       </c>
       <c r="T4" s="0">
-        <v>-15.053337886935381</v>
+        <v>-15.053337886935392</v>
       </c>
       <c r="U4" s="0">
+        <v>-15.053337886935358</v>
+      </c>
+      <c r="V4" s="0">
         <v>1.2881262992720548</v>
       </c>
-      <c r="V4" s="0">
+      <c r="W4" s="0">
         <v>2.0312327785922815</v>
-      </c>
-      <c r="W4" s="0">
-        <v>2.0677425910075642</v>
       </c>
       <c r="X4" s="0">
         <v>2.0677425910075642</v>
       </c>
       <c r="Y4" s="0">
-        <v>2.0577322380427256</v>
+        <v>2.0677425910075642</v>
       </c>
       <c r="Z4" s="0">
-        <v>1</v>
+        <v>2.0954238897540365</v>
       </c>
       <c r="AA4" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="0">
         <v>2</v>
@@ -1116,10 +1142,10 @@
         <v>2</v>
       </c>
       <c r="AE4" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF4" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="0">
         <v>2</v>
@@ -1131,25 +1157,25 @@
         <v>2</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="0">
         <v>4</v>
-      </c>
-      <c r="AL4" s="0">
-        <v>8</v>
       </c>
       <c r="AM4" s="0">
         <v>8</v>
       </c>
       <c r="AN4" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO4" s="0">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="AP4" s="0">
-        <v>88.932806324110672</v>
+        <v>100</v>
       </c>
       <c r="AQ4" s="0">
         <v>88.932806324110672</v>
@@ -1158,91 +1184,97 @@
         <v>88.932806324110672</v>
       </c>
       <c r="AS4" s="0">
-        <v>88.537549407114625</v>
+        <v>88.932806324110672</v>
       </c>
       <c r="AT4" s="0">
-        <v>88.656126482213452</v>
+        <v>88.932806324110672</v>
       </c>
       <c r="AU4" s="0">
         <v>88.656126482213452</v>
       </c>
       <c r="AV4" s="0">
-        <v>88.359683794466406</v>
+        <v>88.656126482213452</v>
       </c>
       <c r="AW4" s="0">
-        <v>4</v>
+        <v>88.507905138339922</v>
       </c>
       <c r="AX4" s="0">
         <v>4</v>
       </c>
       <c r="AY4" s="0">
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="0">
         <v>8</v>
       </c>
-      <c r="AZ4" s="0">
-        <v>0</v>
-      </c>
       <c r="BA4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="0">
         <v>0.039444444444444442</v>
       </c>
-      <c r="BC4" s="0">
+      <c r="BD4" s="0">
         <v>92.490118577075094</v>
       </c>
-      <c r="BD4" s="0">
-        <v>0</v>
-      </c>
       <c r="BE4" s="0">
+        <v>96.245059288537547</v>
+      </c>
+      <c r="BF4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="0">
         <v>12.309894124308629</v>
       </c>
-      <c r="BF4" s="0">
+      <c r="BH4" s="0">
         <v>13.559602336050602</v>
       </c>
-      <c r="BG4" s="0">
+      <c r="BI4" s="0">
         <v>13.559602336050602</v>
       </c>
-      <c r="BH4" s="0">
-        <v>12.918845302627545</v>
-      </c>
-      <c r="BI4" s="0">
-        <v>0</v>
-      </c>
       <c r="BJ4" s="0">
+        <v>14.594739269984869</v>
+      </c>
+      <c r="BK4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="0">
         <v>13.474683879572547</v>
       </c>
-      <c r="BK4" s="0">
+      <c r="BM4" s="0">
         <v>13.502200705461775</v>
       </c>
-      <c r="BL4" s="0">
+      <c r="BN4" s="0">
         <v>13.502200705461775</v>
       </c>
-      <c r="BM4" s="0">
-        <v>13.502200705461787</v>
-      </c>
-      <c r="BN4" s="0">
-        <v>0</v>
-      </c>
       <c r="BO4" s="0">
+        <v>13.502200705461808</v>
+      </c>
+      <c r="BP4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BQ4" s="0">
         <v>0.74310647932022666</v>
       </c>
-      <c r="BP4" s="0">
+      <c r="BR4" s="0">
         <v>0.77961629173550939</v>
       </c>
-      <c r="BQ4" s="0">
+      <c r="BS4" s="0">
         <v>0.77961629173550939</v>
       </c>
-      <c r="BR4" s="0">
-        <v>0.76960593877067085</v>
-      </c>
-      <c r="BS4" s="0">
-        <v>-0.64075703342305612</v>
-      </c>
       <c r="BT4" s="0">
-        <v>1.1102230246251565e-14</v>
+        <v>0.80729759048198169</v>
       </c>
       <c r="BU4" s="0">
-        <v>-0.010010352964838543</v>
+        <v>1.0351369339342664</v>
+      </c>
+      <c r="BV4" s="0">
+        <v>3.3306690738754696e-14</v>
+      </c>
+      <c r="BW4" s="0">
+        <v>0.027681298746472294</v>
       </c>
     </row>
     <row r="5">
@@ -1277,7 +1309,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="0">
-        <v>27.415609054036128</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="0">
         <v>27.415609054036128</v>
@@ -1289,10 +1321,10 @@
         <v>27.415609054036128</v>
       </c>
       <c r="O5" s="0">
-        <v>29.244015328721495</v>
+        <v>27.415609054036128</v>
       </c>
       <c r="P5" s="0">
-        <v>-10.851164422211756</v>
+        <v>27.415609054036128</v>
       </c>
       <c r="Q5" s="0">
         <v>-10.851164422211756</v>
@@ -1307,7 +1339,7 @@
         <v>-10.851164422211756</v>
       </c>
       <c r="U5" s="0">
-        <v>1.4213058130654794</v>
+        <v>-10.851164422211756</v>
       </c>
       <c r="V5" s="0">
         <v>1.4213058130654794</v>
@@ -1319,13 +1351,13 @@
         <v>1.4213058130654794</v>
       </c>
       <c r="Y5" s="0">
-        <v>1.5041951855948956</v>
+        <v>1.4213058130654794</v>
       </c>
       <c r="Z5" s="0">
-        <v>1</v>
+        <v>1.4213058130654794</v>
       </c>
       <c r="AA5" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="0">
         <v>0</v>
@@ -1367,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="0">
         <v>100</v>
@@ -1391,7 +1423,7 @@
         <v>100</v>
       </c>
       <c r="AW5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX5" s="0">
         <v>0</v>
@@ -1403,19 +1435,19 @@
         <v>0</v>
       </c>
       <c r="BA5" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="0">
         <v>0.625</v>
       </c>
-      <c r="BB5" s="0">
+      <c r="BC5" s="0">
         <v>0.011904761904761904</v>
       </c>
-      <c r="BC5" s="0">
-        <v>100</v>
-      </c>
       <c r="BD5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF5" s="0">
         <v>0</v>
@@ -1424,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="BH5" s="0">
-        <v>1.828406274685368</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="0">
         <v>0</v>
@@ -1454,16 +1486,22 @@
         <v>0</v>
       </c>
       <c r="BR5" s="0">
-        <v>0.082889372529416194</v>
+        <v>0</v>
       </c>
       <c r="BS5" s="0">
-        <v>1.828406274685368</v>
+        <v>0</v>
       </c>
       <c r="BT5" s="0">
         <v>0</v>
       </c>
       <c r="BU5" s="0">
-        <v>0.082889372529416194</v>
+        <v>0</v>
+      </c>
+      <c r="BV5" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW5" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1498,55 +1536,55 @@
         <v>5</v>
       </c>
       <c r="K6" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="0">
         <v>-32.57679027558499</v>
       </c>
-      <c r="L6" s="0">
+      <c r="M6" s="0">
         <v>-26.751064878716647</v>
-      </c>
-      <c r="M6" s="0">
-        <v>-27.435422075982295</v>
       </c>
       <c r="N6" s="0">
         <v>-27.435422075982295</v>
       </c>
       <c r="O6" s="0">
-        <v>-27.640997173975755</v>
+        <v>-27.435422075982295</v>
       </c>
       <c r="P6" s="0">
+        <v>-27.176801902317106</v>
+      </c>
+      <c r="Q6" s="0">
         <v>-34.82849805487043</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="R6" s="0">
         <v>-29.845656927395403</v>
-      </c>
-      <c r="R6" s="0">
-        <v>-29.836851773078987</v>
       </c>
       <c r="S6" s="0">
         <v>-29.836851773078987</v>
       </c>
       <c r="T6" s="0">
-        <v>-29.836851773078966</v>
+        <v>-29.836851773078987</v>
       </c>
       <c r="U6" s="0">
+        <v>-29.836851773078987</v>
+      </c>
+      <c r="V6" s="0">
         <v>-1.0697619943744303</v>
       </c>
-      <c r="V6" s="0">
+      <c r="W6" s="0">
         <v>-1.0876845923020129</v>
-      </c>
-      <c r="W6" s="0">
-        <v>-1.146901587800407</v>
       </c>
       <c r="X6" s="0">
         <v>-1.146901587800407</v>
       </c>
       <c r="Y6" s="0">
-        <v>-1.1755857800057252</v>
+        <v>-1.146901587800407</v>
       </c>
       <c r="Z6" s="0">
-        <v>1</v>
+        <v>-1.1446392143530872</v>
       </c>
       <c r="AA6" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="0">
         <v>3</v>
@@ -1555,13 +1593,13 @@
         <v>3</v>
       </c>
       <c r="AD6" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE6" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF6" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="0">
         <v>4</v>
@@ -1570,16 +1608,16 @@
         <v>4</v>
       </c>
       <c r="AI6" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="0">
         <v>7</v>
-      </c>
-      <c r="AL6" s="0">
-        <v>18</v>
       </c>
       <c r="AM6" s="0">
         <v>18</v>
@@ -1588,10 +1626,10 @@
         <v>18</v>
       </c>
       <c r="AO6" s="0">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="AP6" s="0">
-        <v>71.314741035856571</v>
+        <v>100</v>
       </c>
       <c r="AQ6" s="0">
         <v>71.314741035856571</v>
@@ -1600,91 +1638,97 @@
         <v>71.314741035856571</v>
       </c>
       <c r="AS6" s="0">
-        <v>68.924302788844628</v>
+        <v>71.314741035856571</v>
       </c>
       <c r="AT6" s="0">
-        <v>70.418326693227101</v>
+        <v>71.314741035856571</v>
       </c>
       <c r="AU6" s="0">
         <v>70.418326693227101</v>
       </c>
       <c r="AV6" s="0">
-        <v>68.326693227091624</v>
+        <v>70.418326693227101</v>
       </c>
       <c r="AW6" s="0">
+        <v>69.372509960159363</v>
+      </c>
+      <c r="AX6" s="0">
         <v>7.4999999999999991</v>
       </c>
-      <c r="AX6" s="0">
-        <v>8.9999999999999982</v>
-      </c>
       <c r="AY6" s="0">
+        <v>8.25</v>
+      </c>
+      <c r="AZ6" s="0">
         <v>18</v>
       </c>
-      <c r="AZ6" s="0">
+      <c r="BA6" s="0">
         <v>2</v>
       </c>
-      <c r="BA6" s="0">
-        <v>1</v>
-      </c>
       <c r="BB6" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC6" s="0">
         <v>0.1005586592178771</v>
       </c>
-      <c r="BC6" s="0">
+      <c r="BD6" s="0">
         <v>82.470119521912352</v>
       </c>
-      <c r="BD6" s="0">
-        <v>0</v>
-      </c>
       <c r="BE6" s="0">
+        <v>91.235059760956176</v>
+      </c>
+      <c r="BF6" s="0">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="0">
         <v>5.825725396868342</v>
       </c>
-      <c r="BF6" s="0">
+      <c r="BH6" s="0">
         <v>5.1413681996026916</v>
       </c>
-      <c r="BG6" s="0">
+      <c r="BI6" s="0">
         <v>5.1413681996026916</v>
       </c>
-      <c r="BH6" s="0">
-        <v>4.9357931016092316</v>
-      </c>
-      <c r="BI6" s="0">
-        <v>0</v>
-      </c>
       <c r="BJ6" s="0">
+        <v>5.3999883732678828</v>
+      </c>
+      <c r="BK6" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="0">
         <v>4.9828411274750239</v>
       </c>
-      <c r="BK6" s="0">
+      <c r="BM6" s="0">
         <v>4.9916462817914393</v>
       </c>
-      <c r="BL6" s="0">
+      <c r="BN6" s="0">
         <v>4.9916462817914393</v>
       </c>
-      <c r="BM6" s="0">
-        <v>4.9916462817914624</v>
-      </c>
-      <c r="BN6" s="0">
-        <v>0</v>
-      </c>
       <c r="BO6" s="0">
+        <v>4.9916462817914393</v>
+      </c>
+      <c r="BP6" s="0">
+        <v>0</v>
+      </c>
+      <c r="BQ6" s="0">
         <v>-0.017922597927582551</v>
       </c>
-      <c r="BP6" s="0">
+      <c r="BR6" s="0">
         <v>-0.077139593425976649</v>
       </c>
-      <c r="BQ6" s="0">
+      <c r="BS6" s="0">
         <v>-0.077139593425976649</v>
       </c>
-      <c r="BR6" s="0">
-        <v>-0.10582378563129491</v>
-      </c>
-      <c r="BS6" s="0">
-        <v>-0.20557509799346008</v>
-      </c>
       <c r="BT6" s="0">
-        <v>2.2204460492503131e-14</v>
+        <v>-0.074877219978656928</v>
       </c>
       <c r="BU6" s="0">
-        <v>-0.02868419220531826</v>
+        <v>0.25862017366519163</v>
+      </c>
+      <c r="BV6" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW6" s="0">
+        <v>0.002262373447319721</v>
       </c>
     </row>
     <row r="7">
@@ -1719,10 +1763,10 @@
         <v>5</v>
       </c>
       <c r="K7" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="0">
         <v>54.774460567246884</v>
-      </c>
-      <c r="L7" s="0">
-        <v>46.535693150408285</v>
       </c>
       <c r="M7" s="0">
         <v>46.535693150408285</v>
@@ -1734,10 +1778,10 @@
         <v>46.535693150408285</v>
       </c>
       <c r="P7" s="0">
+        <v>46.535693150408285</v>
+      </c>
+      <c r="Q7" s="0">
         <v>-10.77979427373389</v>
-      </c>
-      <c r="Q7" s="0">
-        <v>-10.779794273733788</v>
       </c>
       <c r="R7" s="0">
         <v>-10.779794273733788</v>
@@ -1749,10 +1793,10 @@
         <v>-10.779794273733788</v>
       </c>
       <c r="U7" s="0">
+        <v>-10.779794273733788</v>
+      </c>
+      <c r="V7" s="0">
         <v>2.5553125137272699</v>
-      </c>
-      <c r="V7" s="0">
-        <v>2.2928776475801369</v>
       </c>
       <c r="W7" s="0">
         <v>2.2928776475801369</v>
@@ -1764,7 +1808,7 @@
         <v>2.2928776475801369</v>
       </c>
       <c r="Z7" s="0">
-        <v>1</v>
+        <v>2.2928776475801369</v>
       </c>
       <c r="AA7" s="0">
         <v>1</v>
@@ -1779,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="AE7" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" s="0">
         <v>0</v>
@@ -1797,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7" s="0">
         <v>1</v>
@@ -1809,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="AO7" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AP7" s="0">
-        <v>96.799999999999997</v>
+        <v>100</v>
       </c>
       <c r="AQ7" s="0">
         <v>96.799999999999997</v>
@@ -1833,7 +1877,7 @@
         <v>96.799999999999997</v>
       </c>
       <c r="AW7" s="0">
-        <v>1</v>
+        <v>96.799999999999997</v>
       </c>
       <c r="AX7" s="0">
         <v>1</v>
@@ -1842,25 +1886,25 @@
         <v>1</v>
       </c>
       <c r="AZ7" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="0">
         <v>0.375</v>
       </c>
-      <c r="BB7" s="0">
+      <c r="BC7" s="0">
         <v>0.0077479338842975209</v>
       </c>
-      <c r="BC7" s="0">
-        <v>100</v>
-      </c>
       <c r="BD7" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE7" s="0">
-        <v>-8.2387674168385985</v>
+        <v>100</v>
       </c>
       <c r="BF7" s="0">
-        <v>-8.2387674168385985</v>
+        <v>0</v>
       </c>
       <c r="BG7" s="0">
         <v>-8.2387674168385985</v>
@@ -1869,13 +1913,13 @@
         <v>-8.2387674168385985</v>
       </c>
       <c r="BI7" s="0">
-        <v>0</v>
+        <v>-8.2387674168385985</v>
       </c>
       <c r="BJ7" s="0">
-        <v>9.9920072216264089e-14</v>
+        <v>-8.2387674168385985</v>
       </c>
       <c r="BK7" s="0">
-        <v>9.9920072216264089e-14</v>
+        <v>0</v>
       </c>
       <c r="BL7" s="0">
         <v>9.9920072216264089e-14</v>
@@ -1884,13 +1928,13 @@
         <v>9.9920072216264089e-14</v>
       </c>
       <c r="BN7" s="0">
-        <v>0</v>
+        <v>9.9920072216264089e-14</v>
       </c>
       <c r="BO7" s="0">
-        <v>-0.26243486614713296</v>
+        <v>9.9920072216264089e-14</v>
       </c>
       <c r="BP7" s="0">
-        <v>-0.26243486614713296</v>
+        <v>0</v>
       </c>
       <c r="BQ7" s="0">
         <v>-0.26243486614713296</v>
@@ -1899,12 +1943,18 @@
         <v>-0.26243486614713296</v>
       </c>
       <c r="BS7" s="0">
-        <v>0</v>
+        <v>-0.26243486614713296</v>
       </c>
       <c r="BT7" s="0">
-        <v>0</v>
+        <v>-0.26243486614713296</v>
       </c>
       <c r="BU7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BV7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW7" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1940,7 +1990,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="0">
-        <v>25.578174393289043</v>
+        <v>0.5</v>
       </c>
       <c r="L8" s="0">
         <v>25.578174393289043</v>
@@ -1952,10 +2002,10 @@
         <v>25.578174393289043</v>
       </c>
       <c r="O8" s="0">
-        <v>27.739880285073546</v>
+        <v>25.578174393289043</v>
       </c>
       <c r="P8" s="0">
-        <v>-13.557819053325337</v>
+        <v>25.578174393289043</v>
       </c>
       <c r="Q8" s="0">
         <v>-13.557819053325337</v>
@@ -1967,10 +2017,10 @@
         <v>-13.557819053325337</v>
       </c>
       <c r="T8" s="0">
-        <v>-13.557819053325348</v>
+        <v>-13.557819053325337</v>
       </c>
       <c r="U8" s="0">
-        <v>1.3552713153828093</v>
+        <v>-13.557819053325337</v>
       </c>
       <c r="V8" s="0">
         <v>1.3552713153828093</v>
@@ -1982,13 +2032,13 @@
         <v>1.3552713153828093</v>
       </c>
       <c r="Y8" s="0">
-        <v>1.456488171745087</v>
+        <v>1.3552713153828093</v>
       </c>
       <c r="Z8" s="0">
-        <v>1</v>
+        <v>1.3552713153828093</v>
       </c>
       <c r="AA8" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="0">
         <v>0</v>
@@ -2030,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="0">
         <v>100</v>
@@ -2054,7 +2104,7 @@
         <v>100</v>
       </c>
       <c r="AW8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX8" s="0">
         <v>0</v>
@@ -2066,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="BA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="0">
         <v>0.625</v>
       </c>
-      <c r="BB8" s="0">
+      <c r="BC8" s="0">
         <v>0.013888888888888888</v>
       </c>
-      <c r="BC8" s="0">
-        <v>100</v>
-      </c>
       <c r="BD8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF8" s="0">
         <v>0</v>
@@ -2087,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="BH8" s="0">
-        <v>2.1617058917845045</v>
+        <v>0</v>
       </c>
       <c r="BI8" s="0">
         <v>0</v>
@@ -2102,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="BM8" s="0">
-        <v>-1.1102230246251565e-14</v>
+        <v>0</v>
       </c>
       <c r="BN8" s="0">
         <v>0</v>
@@ -2117,16 +2167,22 @@
         <v>0</v>
       </c>
       <c r="BR8" s="0">
-        <v>0.10121685636227773</v>
+        <v>0</v>
       </c>
       <c r="BS8" s="0">
-        <v>2.1617058917845045</v>
+        <v>0</v>
       </c>
       <c r="BT8" s="0">
-        <v>-1.1102230246251565e-14</v>
+        <v>0</v>
       </c>
       <c r="BU8" s="0">
-        <v>0.10121685636227773</v>
+        <v>0</v>
+      </c>
+      <c r="BV8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW8" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2161,28 +2217,28 @@
         <v>5</v>
       </c>
       <c r="K9" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="0">
         <v>20.342273477919193</v>
       </c>
-      <c r="L9" s="0">
+      <c r="M9" s="0">
         <v>17.7045001403892</v>
-      </c>
-      <c r="M9" s="0">
-        <v>18.806089519182791</v>
       </c>
       <c r="N9" s="0">
         <v>18.806089519182791</v>
       </c>
       <c r="O9" s="0">
-        <v>19.03881812854442</v>
+        <v>18.806089519182791</v>
       </c>
       <c r="P9" s="0">
+        <v>18.806089519182791</v>
+      </c>
+      <c r="Q9" s="0">
         <v>-22.768355184633116</v>
       </c>
-      <c r="Q9" s="0">
+      <c r="R9" s="0">
         <v>-24.46118986042929</v>
-      </c>
-      <c r="R9" s="0">
-        <v>-23.754226653098975</v>
       </c>
       <c r="S9" s="0">
         <v>-23.754226653098975</v>
@@ -2191,22 +2247,22 @@
         <v>-23.754226653098975</v>
       </c>
       <c r="U9" s="0">
+        <v>-23.754226653098975</v>
+      </c>
+      <c r="V9" s="0">
         <v>0.90766215046721255</v>
       </c>
-      <c r="V9" s="0">
+      <c r="W9" s="0">
         <v>0.82567676762358833</v>
-      </c>
-      <c r="W9" s="0">
-        <v>0.8706904395313344</v>
       </c>
       <c r="X9" s="0">
         <v>0.8706904395313344</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.87934582343473899</v>
+        <v>0.8706904395313344</v>
       </c>
       <c r="Z9" s="0">
-        <v>1</v>
+        <v>0.8706904395313344</v>
       </c>
       <c r="AA9" s="0">
         <v>1</v>
@@ -2221,10 +2277,10 @@
         <v>1</v>
       </c>
       <c r="AE9" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="0">
         <v>1</v>
@@ -2236,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="0">
         <v>2</v>
-      </c>
-      <c r="AL9" s="0">
-        <v>4</v>
       </c>
       <c r="AM9" s="0">
         <v>4</v>
@@ -2251,10 +2307,10 @@
         <v>4</v>
       </c>
       <c r="AO9" s="0">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="AP9" s="0">
-        <v>94.799999999999997</v>
+        <v>100</v>
       </c>
       <c r="AQ9" s="0">
         <v>94.799999999999997</v>
@@ -2266,7 +2322,7 @@
         <v>94.799999999999997</v>
       </c>
       <c r="AT9" s="0">
-        <v>94.659999999999997</v>
+        <v>94.799999999999997</v>
       </c>
       <c r="AU9" s="0">
         <v>94.659999999999997</v>
@@ -2275,79 +2331,85 @@
         <v>94.659999999999997</v>
       </c>
       <c r="AW9" s="0">
-        <v>2</v>
+        <v>94.659999999999997</v>
       </c>
       <c r="AX9" s="0">
         <v>2</v>
       </c>
       <c r="AY9" s="0">
+        <v>2</v>
+      </c>
+      <c r="AZ9" s="0">
         <v>4</v>
       </c>
-      <c r="AZ9" s="0">
-        <v>0</v>
-      </c>
       <c r="BA9" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB9" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC9" s="0">
         <v>0.024261603375527425</v>
       </c>
-      <c r="BC9" s="0">
-        <v>100</v>
-      </c>
       <c r="BD9" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE9" s="0">
+        <v>100</v>
+      </c>
+      <c r="BF9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="0">
         <v>-2.6377733375299917</v>
       </c>
-      <c r="BF9" s="0">
+      <c r="BH9" s="0">
         <v>-1.5361839587364035</v>
       </c>
-      <c r="BG9" s="0">
+      <c r="BI9" s="0">
         <v>-1.5361839587364035</v>
       </c>
-      <c r="BH9" s="0">
-        <v>-1.3034553493747714</v>
-      </c>
-      <c r="BI9" s="0">
-        <v>0</v>
-      </c>
       <c r="BJ9" s="0">
+        <v>-1.5361839587364035</v>
+      </c>
+      <c r="BK9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="0">
         <v>-1.6928346757961732</v>
-      </c>
-      <c r="BK9" s="0">
-        <v>-0.98587146846585982</v>
-      </c>
-      <c r="BL9" s="0">
-        <v>-0.98587146846585982</v>
       </c>
       <c r="BM9" s="0">
         <v>-0.98587146846585982</v>
       </c>
       <c r="BN9" s="0">
-        <v>0</v>
+        <v>-0.98587146846585982</v>
       </c>
       <c r="BO9" s="0">
+        <v>-0.98587146846585982</v>
+      </c>
+      <c r="BP9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BQ9" s="0">
         <v>-0.081985382843624222</v>
       </c>
-      <c r="BP9" s="0">
+      <c r="BR9" s="0">
         <v>-0.036971710935878144</v>
       </c>
-      <c r="BQ9" s="0">
+      <c r="BS9" s="0">
         <v>-0.036971710935878144</v>
       </c>
-      <c r="BR9" s="0">
-        <v>-0.028316327032473554</v>
-      </c>
-      <c r="BS9" s="0">
-        <v>0.23272860936163209</v>
-      </c>
       <c r="BT9" s="0">
-        <v>0</v>
+        <v>-0.036971710935878144</v>
       </c>
       <c r="BU9" s="0">
-        <v>0.0086553839034045899</v>
+        <v>0</v>
+      </c>
+      <c r="BV9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW9" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2382,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="0">
-        <v>20.185248490175912</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="0">
         <v>20.185248490175912</v>
@@ -2394,10 +2456,10 @@
         <v>20.185248490175912</v>
       </c>
       <c r="O10" s="0">
-        <v>20.418515135699323</v>
+        <v>20.185248490175912</v>
       </c>
       <c r="P10" s="0">
-        <v>-11.83474937620419</v>
+        <v>20.185248490175912</v>
       </c>
       <c r="Q10" s="0">
         <v>-11.83474937620419</v>
@@ -2412,7 +2474,7 @@
         <v>-11.83474937620419</v>
       </c>
       <c r="U10" s="0">
-        <v>2.6103479861647885</v>
+        <v>-11.83474937620419</v>
       </c>
       <c r="V10" s="0">
         <v>2.6103479861647885</v>
@@ -2424,13 +2486,13 @@
         <v>2.6103479861647885</v>
       </c>
       <c r="Y10" s="0">
-        <v>2.6380030059635273</v>
+        <v>2.6103479861647885</v>
       </c>
       <c r="Z10" s="0">
-        <v>1</v>
+        <v>2.6103479861647885</v>
       </c>
       <c r="AA10" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="0">
         <v>0</v>
@@ -2472,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP10" s="0">
         <v>100</v>
@@ -2496,7 +2558,7 @@
         <v>100</v>
       </c>
       <c r="AW10" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX10" s="0">
         <v>0</v>
@@ -2508,19 +2570,19 @@
         <v>0</v>
       </c>
       <c r="BA10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="0">
         <v>0.125</v>
       </c>
-      <c r="BB10" s="0">
+      <c r="BC10" s="0">
         <v>0.0012254901960784314</v>
       </c>
-      <c r="BC10" s="0">
-        <v>100</v>
-      </c>
       <c r="BD10" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE10" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF10" s="0">
         <v>0</v>
@@ -2529,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="BH10" s="0">
-        <v>0.23326664552341114</v>
+        <v>0</v>
       </c>
       <c r="BI10" s="0">
         <v>0</v>
@@ -2559,16 +2621,22 @@
         <v>0</v>
       </c>
       <c r="BR10" s="0">
-        <v>0.027655019798738856</v>
+        <v>0</v>
       </c>
       <c r="BS10" s="0">
-        <v>0.23326664552341114</v>
+        <v>0</v>
       </c>
       <c r="BT10" s="0">
         <v>0</v>
       </c>
       <c r="BU10" s="0">
-        <v>0.027655019798738856</v>
+        <v>0</v>
+      </c>
+      <c r="BV10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
